--- a/Output/lapop_selection_regressions.xlsx
+++ b/Output/lapop_selection_regressions.xlsx
@@ -1,296 +1,289 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dec977f0560f05bf/BID/Papers Valerie/Ley de nietos/Argentina/Output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_8966933C1D316AB40AE52C5F13BA1C619259D5AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B592A8E-30DC-2142-90DC-CE9BB60F81B8}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="18960" windowHeight="16160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="88">
-  <si>
-    <t>part</t>
-  </si>
-  <si>
-    <t>term</t>
-  </si>
-  <si>
-    <t>statistic</t>
-  </si>
-  <si>
-    <t>Left-right ideology</t>
-  </si>
-  <si>
-    <t>Previous vote</t>
-  </si>
-  <si>
-    <t>Party identification</t>
-  </si>
-  <si>
-    <t>Vote intention</t>
-  </si>
-  <si>
-    <t>Blank/null vote intention</t>
-  </si>
-  <si>
-    <t>Community meetings</t>
-  </si>
-  <si>
-    <t>estimates</t>
-  </si>
-  <si>
-    <t>Intends to migrate</t>
-  </si>
-  <si>
-    <t>estimate</t>
-  </si>
-  <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>-0.097***</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>-0.015</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>0.032*</t>
-  </si>
-  <si>
-    <t>std.error</t>
-  </si>
-  <si>
-    <t>(0.124)</t>
-  </si>
-  <si>
-    <t>(0.024)</t>
-  </si>
-  <si>
-    <t>(0.018)</t>
-  </si>
-  <si>
-    <t>(0.014)</t>
-  </si>
-  <si>
-    <t>(0.017)</t>
-  </si>
-  <si>
-    <t>Intends to migrate × Spanish share 1936–1955</t>
-  </si>
-  <si>
-    <t>0.455***</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>-0.017</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>(0.167)</t>
-  </si>
-  <si>
-    <t>(0.036)</t>
-  </si>
-  <si>
-    <t>(0.027)</t>
-  </si>
-  <si>
-    <t>(0.028)</t>
-  </si>
-  <si>
-    <t>(0.026)</t>
-  </si>
-  <si>
-    <t>(0.034)</t>
-  </si>
-  <si>
-    <t>Intends to migrate × Spanish share 1956–1978</t>
-  </si>
-  <si>
-    <t>-2.138***</t>
-  </si>
-  <si>
-    <t>-0.276</t>
-  </si>
-  <si>
-    <t>-0.005</t>
-  </si>
-  <si>
-    <t>-0.179</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>(0.595)</t>
-  </si>
-  <si>
-    <t>(0.172)</t>
-  </si>
-  <si>
-    <t>(0.115)</t>
-  </si>
-  <si>
-    <t>(0.114)</t>
-  </si>
-  <si>
-    <t>(0.128)</t>
-  </si>
-  <si>
-    <t>(0.137)</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>0.014***</t>
-  </si>
-  <si>
-    <t>0.004***</t>
-  </si>
-  <si>
-    <t>-0.002***</t>
-  </si>
-  <si>
-    <t>0.001***</t>
-  </si>
-  <si>
-    <t>(0.002)</t>
-  </si>
-  <si>
-    <t>(0.000)</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>-0.074</t>
-  </si>
-  <si>
-    <t>-0.006</t>
-  </si>
-  <si>
-    <t>0.033***</t>
-  </si>
-  <si>
-    <t>-0.003</t>
-  </si>
-  <si>
-    <t>-0.010</t>
-  </si>
-  <si>
-    <t>(0.066)</t>
-  </si>
-  <si>
-    <t>(0.010)</t>
-  </si>
-  <si>
-    <t>(0.011)</t>
-  </si>
-  <si>
-    <t>(0.007)</t>
-  </si>
-  <si>
-    <t>Years of education</t>
-  </si>
-  <si>
-    <t>-0.013</t>
-  </si>
-  <si>
-    <t>0.007***</t>
-  </si>
-  <si>
-    <t>-0.015***</t>
-  </si>
-  <si>
-    <t>0.005***</t>
-  </si>
-  <si>
-    <t>gof</t>
-  </si>
-  <si>
-    <t>Num.Obs.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>4802</t>
-  </si>
-  <si>
-    <t>5748</t>
-  </si>
-  <si>
-    <t>5687</t>
-  </si>
-  <si>
-    <t>4953</t>
-  </si>
-  <si>
-    <t>4426</t>
-  </si>
-  <si>
-    <t>5752</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>0.022</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+  <si>
+    <t xml:space="preserve">part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left-right ideology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous vote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vote intention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blank/null vote intention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community meetings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intends to migrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.097***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">std.error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intends to migrate × Spanish share 1936–1955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.167)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intends to migrate × Spanish share 1956–1978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.138***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.595)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.172)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.114)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.128)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.137)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.002***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.066)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years of education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.015***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num.Obs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -326,15 +319,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -616,14 +600,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -681,7 +662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -710,7 +691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -739,7 +720,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -768,7 +749,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -797,7 +778,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -826,7 +807,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -855,7 +836,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -884,7 +865,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -913,7 +894,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -942,7 +923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -971,7 +952,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1000,7 +981,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -1029,7 +1010,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -1060,6 +1041,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>